--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU02/HRM/post FET_HRM-2031-0132/Panel 7/Coupon back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU02_Coupon_Back_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU02/HRM/post FET_HRM-2031-0132/Panel 7/Coupon back/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU02_Coupon_Back_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.84364</v>
+        <v>16.99754</v>
       </c>
       <c r="D2" t="n">
-        <v>16.50068</v>
+        <v>16.68218</v>
       </c>
       <c r="E2" t="n">
-        <v>16.54608</v>
+        <v>16.68596</v>
       </c>
       <c r="F2" t="n">
-        <v>40.9419</v>
+        <v>42.30573</v>
       </c>
       <c r="G2" t="n">
-        <v>0.04962</v>
+        <v>0.05064</v>
       </c>
       <c r="H2" t="n">
-        <v>1.79981</v>
+        <v>1.82196</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.8238</v>
+        <v>16.9551</v>
       </c>
       <c r="D3" t="n">
-        <v>16.64374</v>
+        <v>16.81113</v>
       </c>
       <c r="E3" t="n">
-        <v>16.72025</v>
+        <v>16.90515</v>
       </c>
       <c r="F3" t="n">
-        <v>42.24996</v>
+        <v>42.97742</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05134</v>
+        <v>0.05049</v>
       </c>
       <c r="H3" t="n">
-        <v>1.81162</v>
+        <v>1.84101</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16.84911</v>
+        <v>16.91639</v>
       </c>
       <c r="D4" t="n">
-        <v>16.43803</v>
+        <v>16.47281</v>
       </c>
       <c r="E4" t="n">
-        <v>16.91242</v>
+        <v>16.68429</v>
       </c>
       <c r="F4" t="n">
-        <v>42.24749</v>
+        <v>42.6207</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05091</v>
+        <v>0.04971</v>
       </c>
       <c r="H4" t="n">
-        <v>1.83502</v>
+        <v>1.83721</v>
       </c>
     </row>
     <row r="5">
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.58668</v>
+        <v>16.76483</v>
       </c>
       <c r="D6" t="n">
-        <v>16.01236</v>
+        <v>16.02052</v>
       </c>
       <c r="E6" t="n">
-        <v>16.41407</v>
+        <v>16.07527</v>
       </c>
       <c r="F6" t="n">
-        <v>21.72565</v>
+        <v>21.91674</v>
       </c>
       <c r="G6" t="n">
-        <v>33.94939</v>
+        <v>33.14787</v>
       </c>
     </row>
     <row r="7">
@@ -589,19 +589,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.58931</v>
+        <v>16.53904</v>
       </c>
       <c r="D7" t="n">
-        <v>15.81119</v>
+        <v>15.9212</v>
       </c>
       <c r="E7" t="n">
-        <v>16.46675</v>
+        <v>16.30586</v>
       </c>
       <c r="F7" t="n">
-        <v>21.78328</v>
+        <v>21.80757</v>
       </c>
       <c r="G7" t="n">
-        <v>33.70048</v>
+        <v>34.15808</v>
       </c>
     </row>
     <row r="8">
@@ -611,19 +611,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.83257</v>
+        <v>16.79065</v>
       </c>
       <c r="D8" t="n">
-        <v>16.04789</v>
+        <v>16.18312</v>
       </c>
       <c r="E8" t="n">
-        <v>16.40475</v>
+        <v>16.2131</v>
       </c>
       <c r="F8" t="n">
-        <v>21.89882</v>
+        <v>22.05685</v>
       </c>
       <c r="G8" t="n">
-        <v>34.37978</v>
+        <v>33.95963</v>
       </c>
     </row>
   </sheetData>
